--- a/erp-server/erp-server-wms/src/main/resources/excel/overseasDeliveryPlan.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/overseasDeliveryPlan.xlsx
@@ -16,15 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>单据编号</t>
   </si>
   <si>
     <t>审核状态</t>
-  </si>
-  <si>
-    <t>作废状态</t>
   </si>
   <si>
     <t>发货状态</t>
@@ -70,9 +67,6 @@
   </si>
   <si>
     <t>{.approveStatusName}</t>
-  </si>
-  <si>
-    <t>{.invalidStatusName}</t>
   </si>
   <si>
     <t>{.deliveryStatusName}</t>
@@ -1126,28 +1120,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:WPL2"/>
+  <dimension ref="A1:WPK2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="8.5" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="12.375" customWidth="1"/>
-    <col min="6" max="6" width="24.125" customWidth="1"/>
-    <col min="7" max="7" width="7.375" customWidth="1"/>
-    <col min="8" max="8" width="14.375" customWidth="1"/>
-    <col min="9" max="9" width="31.5" customWidth="1"/>
-    <col min="10" max="10" width="10.25" customWidth="1"/>
-    <col min="11" max="11" width="9.5" customWidth="1"/>
-    <col min="12" max="13" width="10.25" customWidth="1"/>
-    <col min="14" max="14" width="9.625" customWidth="1"/>
-    <col min="15" max="15" width="17.25" customWidth="1"/>
-    <col min="16" max="16" width="18.375" customWidth="1"/>
-    <col min="17" max="220" width="9" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="12.375" customWidth="1"/>
+    <col min="5" max="5" width="24.125" customWidth="1"/>
+    <col min="6" max="6" width="7.375" customWidth="1"/>
+    <col min="7" max="7" width="14.375" customWidth="1"/>
+    <col min="8" max="8" width="31.5" customWidth="1"/>
+    <col min="9" max="9" width="10.25" customWidth="1"/>
+    <col min="10" max="10" width="9.5" customWidth="1"/>
+    <col min="11" max="12" width="10.25" customWidth="1"/>
+    <col min="13" max="13" width="9.625" customWidth="1"/>
+    <col min="14" max="14" width="17.25" customWidth="1"/>
+    <col min="15" max="15" width="18.375" customWidth="1"/>
+    <col min="16" max="219" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1163,7 +1156,7 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
@@ -1193,59 +1186,54 @@
       <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:15975">
+      <c r="A2" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:15976">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="O2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>31</v>
-      </c>
+      <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
       <c r="S2" s="4"/>
@@ -17205,7 +17193,6 @@
       <c r="WPI2" s="4"/>
       <c r="WPJ2" s="4"/>
       <c r="WPK2" s="4"/>
-      <c r="WPL2" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-wms/src/main/resources/excel/overseasDeliveryPlan.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/overseasDeliveryPlan.xlsx
@@ -4,19 +4,32 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>单据编号</t>
   </si>
@@ -34,6 +47,21 @@
   </si>
   <si>
     <t>国家</t>
+  </si>
+  <si>
+    <r>
+      <t>第三方仓</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF5F826B"/>
+        <rFont val="Courier New"/>
+        <charset val="134"/>
+      </rPr>
+      <t>SKU</t>
+    </r>
   </si>
   <si>
     <t>产品编号</t>
@@ -81,6 +109,9 @@
     <t>{.countryName}</t>
   </si>
   <si>
+    <t>{.thirdWarehouseSku}</t>
+  </si>
+  <si>
     <t>{.skuNo}</t>
   </si>
   <si>
@@ -111,14 +142,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -276,6 +307,13 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF5F826B"/>
+      <name val="Courier New"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1120,7 +1158,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:WPK2"/>
+  <dimension ref="A1:WPL2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1129,18 +1167,19 @@
     <col min="4" max="4" width="12.375" customWidth="1"/>
     <col min="5" max="5" width="24.125" customWidth="1"/>
     <col min="6" max="6" width="7.375" customWidth="1"/>
-    <col min="7" max="7" width="14.375" customWidth="1"/>
-    <col min="8" max="8" width="31.5" customWidth="1"/>
-    <col min="9" max="9" width="10.25" customWidth="1"/>
-    <col min="10" max="10" width="9.5" customWidth="1"/>
-    <col min="11" max="12" width="10.25" customWidth="1"/>
-    <col min="13" max="13" width="9.625" customWidth="1"/>
-    <col min="14" max="14" width="17.25" customWidth="1"/>
-    <col min="15" max="15" width="18.375" customWidth="1"/>
-    <col min="16" max="219" width="9" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="16.375" customWidth="1"/>
+    <col min="8" max="8" width="14.375" customWidth="1"/>
+    <col min="9" max="9" width="31.5" customWidth="1"/>
+    <col min="10" max="10" width="10.25" customWidth="1"/>
+    <col min="11" max="11" width="9.5" customWidth="1"/>
+    <col min="12" max="13" width="10.25" customWidth="1"/>
+    <col min="14" max="14" width="9.625" customWidth="1"/>
+    <col min="15" max="15" width="17.25" customWidth="1"/>
+    <col min="16" max="16" width="18.375" customWidth="1"/>
+    <col min="17" max="220" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1159,7 +1198,7 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="3" t="s">
@@ -1186,54 +1225,59 @@
       <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:15975">
-      <c r="A2" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="2" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:15976">
+      <c r="A2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="P2" s="4"/>
+      <c r="O2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
       <c r="S2" s="4"/>
@@ -17193,6 +17237,7 @@
       <c r="WPI2" s="4"/>
       <c r="WPJ2" s="4"/>
       <c r="WPK2" s="4"/>
+      <c r="WPL2" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
